--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-regression-CYC-2/03-test-cases/CYC-2-test-cases.xlsx
@@ -3360,7 +3360,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:31.643Z</t>
+    <t>2026-10-05T16:44:19.314Z</t>
   </si>
   <si>
     <t>Column order</t>
